--- a/assets/constructions/examples/ctd_tthi_holder.xlsx
+++ b/assets/constructions/examples/ctd_tthi_holder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,24 +619,40 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AVRC25D-4LH</t>
+          <t>S40V STGP R 22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AVRC</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>N</t>
@@ -648,74 +664,74 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TPMC 2204..</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ISO_5609:25</t>
+          <t>ISO_5609:40</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>VARGUS_1/2IL</t>
+          <t>PALB_TP22</t>
         </is>
       </c>
       <c r="L2" t="n">
         <v>10</v>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>4.1</v>
+      </c>
       <c r="N2" t="n">
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>32</v>
+        <v>78.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="U2" t="n">
         <v>3</v>
       </c>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="b">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>29.7</v>
-      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>100</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
@@ -728,8 +744,22 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2022/VARGUS Catalog VARDEX</t>
-        </is>
+          <t>2022/ palbit основной каталог.pdf</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>554.37</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>50965.29</v>
       </c>
     </row>
     <row r="3">
@@ -740,7 +770,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVRC50-5MG20ISO</t>
+          <t>NVR16D-3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -750,7 +780,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NVRC</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -765,7 +795,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>VAR_5MGI20_H</t>
+          <t>VAR_IC3/8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -773,39 +803,35 @@
           <t>VARGUS</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5MGIR20.0ISO...</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ISO_5609:50</t>
+          <t>ISO_5609:16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>VARGUS_5MGIR20.0ISO</t>
+          <t>VARGUS_3/8IR</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>70.40000000000001</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="R3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -823,32 +849,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
-        <v>50</v>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>46.5</v>
+        <v>11.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>257.5</v>
+        <v>150</v>
       </c>
       <c r="AG3" t="n">
-        <v>125</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>49.7</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
           <t>STL</t>
@@ -862,6 +884,20 @@
         <is>
           <t>2018/VARGUS Catalog VARDEX</t>
         </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>7612.11</v>
       </c>
     </row>
     <row r="4">
@@ -872,17 +908,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BNVRC10M-6.0KLH</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
+          <t>NVRC10D-2LH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BNVRC</t>
+          <t>NVRC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -897,7 +929,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>VAR_6.0</t>
+          <t>VAR_IC1/4</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -913,7 +945,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>VARGUS_6.0KIL</t>
+          <t>VARGUS_1/4IL</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -921,21 +953,19 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>13</v>
+      </c>
       <c r="Q4" t="n">
         <v>10</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t>L</t>
@@ -945,9 +975,7 @@
         <v>3</v>
       </c>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="b">
-        <v>0</v>
-      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
         <v>1</v>
       </c>
@@ -961,12 +989,14 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>12.3</v>
+      </c>
       <c r="AF4" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
@@ -980,8 +1010,22 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2018/VARGUS Catalog VARDEX</t>
-        </is>
+          <t>2022/VARGUS Catalog VARDEX</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>8851.379999999999</v>
       </c>
     </row>
     <row r="5">
@@ -992,17 +1036,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OVR16D-2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
+          <t>NVRC10-2X</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>NVRC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1015,11 +1055,7 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>VAR_IC1/4</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>VARGUS</t>
@@ -1028,12 +1064,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ISO_5609:16</t>
+          <t>ISO_5609:20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>VARGUS_1/4IR</t>
+          <t>VARGUS_1/4XIR</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1046,16 +1082,14 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>13</v>
+      </c>
       <c r="Q5" t="n">
-        <v>16</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>R</t>
@@ -1065,30 +1099,30 @@
         <v>3</v>
       </c>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="b">
-        <v>0</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>18</v>
+      </c>
       <c r="AE5" t="n">
-        <v>8.9</v>
+        <v>12.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="AG5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
@@ -1102,27 +1136,37 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2018/VARGUS Catalog VARDEX</t>
-        </is>
+          <t>2022/VARGUS Catalog VARDEX</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>8851.379999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AVRC20-3X</t>
+          <t>SIL0025Q16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AVRC</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>N</t>
@@ -1136,71 +1180,65 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ISO_5609:20</t>
+          <t>ISO_5609:25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>VARGUS_3/8XIR</t>
+          <t>DER_16_IL</t>
         </is>
       </c>
       <c r="L6" t="n">
         <v>10</v>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="P6" t="n">
-        <v>24</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>3</v>
       </c>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
         <v>180</v>
       </c>
       <c r="AG6" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
@@ -1214,9 +1252,15 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2022/VARGUS Catalog VARDEX</t>
-        </is>
-      </c>
+          <t>Специнструмент</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
